--- a/ms6_BatchExport_input_v3.xlsx
+++ b/ms6_BatchExport_input_v3.xlsx
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
